--- a/(100826)TEMPLATE_DATA FOR DASHBOARD_V1.xlsx
+++ b/(100826)TEMPLATE_DATA FOR DASHBOARD_V1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nykgroup-my.sharepoint.com/personal/nguyenbich_ngoc_nykgroup_com/Documents/CS standard time_Claude/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1324" documentId="8_{F9537D5D-B12A-4A4C-AF40-128E8D45C306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55C16DA3-0888-428F-A9B0-401002B4DDF9}"/>
+  <xr:revisionPtr revIDLastSave="1335" documentId="8_{F9537D5D-B12A-4A4C-AF40-128E8D45C306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AB8D802-DDA9-4BDA-98DA-3AB46C5AC2B2}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="932" xr2:uid="{E21F554E-3F05-4DDC-8BE4-80952248A30F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="932" activeTab="15" xr2:uid="{E21F554E-3F05-4DDC-8BE4-80952248A30F}"/>
   </bookViews>
   <sheets>
     <sheet name="HC" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,15 @@
     <sheet name="YVF" sheetId="20" r:id="rId5"/>
     <sheet name="Shipment volume" sheetId="2" r:id="rId6"/>
     <sheet name="Customer Volume-N&amp;S" sheetId="6" r:id="rId7"/>
-    <sheet name="Customer Volume - HAD" sheetId="16" r:id="rId8"/>
-    <sheet name="Customer Volume - HAN" sheetId="17" r:id="rId9"/>
-    <sheet name="Customer Volume - HLC" sheetId="18" r:id="rId10"/>
-    <sheet name="Customer Volume - HCM" sheetId="19" r:id="rId11"/>
+    <sheet name="Customer Volume - HAD" sheetId="16" state="hidden" r:id="rId8"/>
+    <sheet name="Customer Volume - HAN" sheetId="17" state="hidden" r:id="rId9"/>
+    <sheet name="Customer Volume - HLC" sheetId="18" state="hidden" r:id="rId10"/>
+    <sheet name="Customer Volume - HCM" sheetId="19" state="hidden" r:id="rId11"/>
     <sheet name="C" sheetId="11" r:id="rId12"/>
     <sheet name="A" sheetId="12" r:id="rId13"/>
     <sheet name="S" sheetId="13" r:id="rId14"/>
     <sheet name="E" sheetId="14" r:id="rId15"/>
+    <sheet name="Ghi chú" sheetId="22" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Customer Volume-N&amp;S'!$A$2:$P$1163</definedName>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5538" uniqueCount="1396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5745" uniqueCount="1600">
   <si>
     <t>Total</t>
   </si>
@@ -4250,6 +4251,618 @@
   </si>
   <si>
     <t>Overal  Workload Status</t>
+  </si>
+  <si>
+    <t>Scope of Job</t>
+  </si>
+  <si>
+    <t>CTAW</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + Air + B.Warehouse</t>
+  </si>
+  <si>
+    <t>CTOW</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + Ocean + B.Warehouse</t>
+  </si>
+  <si>
+    <t>CTOB</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + Ocean</t>
+  </si>
+  <si>
+    <t>CTAB</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + Air</t>
+  </si>
+  <si>
+    <t>CTWB</t>
+  </si>
+  <si>
+    <t>Customs + Trucking +B. Warehouse</t>
+  </si>
+  <si>
+    <t>CTRB</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + Rail</t>
+  </si>
+  <si>
+    <t>CAWB</t>
+  </si>
+  <si>
+    <t>Customs + Air + B.Warehouse</t>
+  </si>
+  <si>
+    <t>COWB</t>
+  </si>
+  <si>
+    <t>Customs + Ocean + B.Warehouse</t>
+  </si>
+  <si>
+    <t>CTBB</t>
+  </si>
+  <si>
+    <t>Customs + Trucking</t>
+  </si>
+  <si>
+    <t>CWBB</t>
+  </si>
+  <si>
+    <t>Customs +B. Warehouse</t>
+  </si>
+  <si>
+    <t>COBB</t>
+  </si>
+  <si>
+    <t>Customs + Ocean</t>
+  </si>
+  <si>
+    <t>CABB</t>
+  </si>
+  <si>
+    <t>Customs + Air</t>
+  </si>
+  <si>
+    <t>CTCR</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + Cross-Border Rail</t>
+  </si>
+  <si>
+    <t>CRBB</t>
+  </si>
+  <si>
+    <t>Customs + Rail</t>
+  </si>
+  <si>
+    <t>CARB</t>
+  </si>
+  <si>
+    <t>Customs + Air + Rail</t>
+  </si>
+  <si>
+    <t>CWRB</t>
+  </si>
+  <si>
+    <t>Customs + B.Warehouse + Rail</t>
+  </si>
+  <si>
+    <t>CORB</t>
+  </si>
+  <si>
+    <t>Customs + Ocean + Rail</t>
+  </si>
+  <si>
+    <t>COWR</t>
+  </si>
+  <si>
+    <t>Customs + Ocean + B.Warehouse + Rail</t>
+  </si>
+  <si>
+    <t>TAWB</t>
+  </si>
+  <si>
+    <t>Trucking + Air + B.Warehouse</t>
+  </si>
+  <si>
+    <t>TOBB</t>
+  </si>
+  <si>
+    <t>Trucking + Ocean</t>
+  </si>
+  <si>
+    <t>TOWB</t>
+  </si>
+  <si>
+    <t>Trucking + Ocean +B.Warehouse</t>
+  </si>
+  <si>
+    <t>TABB</t>
+  </si>
+  <si>
+    <t>Trucking + Air</t>
+  </si>
+  <si>
+    <t>TBBB</t>
+  </si>
+  <si>
+    <t>Trucking Only</t>
+  </si>
+  <si>
+    <t>TWBB</t>
+  </si>
+  <si>
+    <t>Trucking +B.Warehouse</t>
+  </si>
+  <si>
+    <t>TRBB</t>
+  </si>
+  <si>
+    <t>Trucking + Rail</t>
+  </si>
+  <si>
+    <t>TAOB</t>
+  </si>
+  <si>
+    <t>Trucking + Air + Ocean</t>
+  </si>
+  <si>
+    <t>TARB</t>
+  </si>
+  <si>
+    <t>Trucking + Air + Rail</t>
+  </si>
+  <si>
+    <t>TORB</t>
+  </si>
+  <si>
+    <t>Trucking + Ocean + Rail</t>
+  </si>
+  <si>
+    <t>TWRB</t>
+  </si>
+  <si>
+    <t>Trucking +B.Warehouse + Rail</t>
+  </si>
+  <si>
+    <t>UBBB</t>
+  </si>
+  <si>
+    <t>Trucking Round-Use</t>
+  </si>
+  <si>
+    <t>MBBB</t>
+  </si>
+  <si>
+    <t>Trucking Milkrun/Shuttle</t>
+  </si>
+  <si>
+    <t>ABBB</t>
+  </si>
+  <si>
+    <t>Air Freight Only</t>
+  </si>
+  <si>
+    <t>OBBB</t>
+  </si>
+  <si>
+    <t>Ocean Freight Only</t>
+  </si>
+  <si>
+    <t>WBBB</t>
+  </si>
+  <si>
+    <t>B.Warehouse Only</t>
+  </si>
+  <si>
+    <t>RBBB</t>
+  </si>
+  <si>
+    <t>Rail Only</t>
+  </si>
+  <si>
+    <t>AWBB</t>
+  </si>
+  <si>
+    <t>Air + B.Warehouse</t>
+  </si>
+  <si>
+    <t>OWBB</t>
+  </si>
+  <si>
+    <t>Ocean +B. Warehouse</t>
+  </si>
+  <si>
+    <t>ARBB</t>
+  </si>
+  <si>
+    <t>Air + Rail</t>
+  </si>
+  <si>
+    <t>ORBB</t>
+  </si>
+  <si>
+    <t>Ocean + Rail</t>
+  </si>
+  <si>
+    <t>WRBB</t>
+  </si>
+  <si>
+    <t>B.Warehouse + Rail</t>
+  </si>
+  <si>
+    <t>AWRB</t>
+  </si>
+  <si>
+    <t>Air + B.Warehouse + Rail</t>
+  </si>
+  <si>
+    <t>OWRB</t>
+  </si>
+  <si>
+    <t>Ocean +B. Warehouse + Rail</t>
+  </si>
+  <si>
+    <t>CBTB</t>
+  </si>
+  <si>
+    <t>Cross-Border Truck</t>
+  </si>
+  <si>
+    <t>CBTW</t>
+  </si>
+  <si>
+    <t>Cross-Border + B.Warehouse</t>
+  </si>
+  <si>
+    <t>CBTA</t>
+  </si>
+  <si>
+    <t>Cross-Border Truck + Air</t>
+  </si>
+  <si>
+    <t>CBTO</t>
+  </si>
+  <si>
+    <t>Cross-Border + Ocean</t>
+  </si>
+  <si>
+    <t>CBRB</t>
+  </si>
+  <si>
+    <t>Cross-Border Rail</t>
+  </si>
+  <si>
+    <t>BCLC</t>
+  </si>
+  <si>
+    <t>Buyer Consol (Cross-Border Truck/Rail)</t>
+  </si>
+  <si>
+    <t>BCLO</t>
+  </si>
+  <si>
+    <t>Buyer Consol (Ocean)</t>
+  </si>
+  <si>
+    <t>APRB</t>
+  </si>
+  <si>
+    <t>Air Charter</t>
+  </si>
+  <si>
+    <t>CBBB</t>
+  </si>
+  <si>
+    <t>Customs Only</t>
+  </si>
+  <si>
+    <t>BBBB</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>IBBB</t>
+  </si>
+  <si>
+    <t>Trouble-shooting Handling</t>
+  </si>
+  <si>
+    <t>FCTB</t>
+  </si>
+  <si>
+    <t>Booking Agent + Customs + Truck</t>
+  </si>
+  <si>
+    <t>FTBB</t>
+  </si>
+  <si>
+    <t>Booking Agent + Truck</t>
+  </si>
+  <si>
+    <t>FCBB</t>
+  </si>
+  <si>
+    <t>Booking Agent + Customs</t>
+  </si>
+  <si>
+    <t>FWBB</t>
+  </si>
+  <si>
+    <t>Booking Agent +B. Warehouse</t>
+  </si>
+  <si>
+    <t>FTWB</t>
+  </si>
+  <si>
+    <t>Booking Agent + Truck +B. Warehouse</t>
+  </si>
+  <si>
+    <t>FCWB</t>
+  </si>
+  <si>
+    <t>Booking Agent + Customs +B. Warehouse</t>
+  </si>
+  <si>
+    <t>FCTW</t>
+  </si>
+  <si>
+    <t>Booking Agent + Customs + Truck +B. Warehouse</t>
+  </si>
+  <si>
+    <t>FBBB</t>
+  </si>
+  <si>
+    <t>Booking Agent</t>
+  </si>
+  <si>
+    <t>VBBB</t>
+  </si>
+  <si>
+    <t>Vendor Booking Release</t>
+  </si>
+  <si>
+    <t>DBBB</t>
+  </si>
+  <si>
+    <t>Vendor Doc</t>
+  </si>
+  <si>
+    <t>CTAS</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + Air + CFS warehouse</t>
+  </si>
+  <si>
+    <t>CTOS</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + Ocean + CFS warehouse</t>
+  </si>
+  <si>
+    <t>CTSB</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + CFS warehouse</t>
+  </si>
+  <si>
+    <t>CASB</t>
+  </si>
+  <si>
+    <t>Customs + Air + CFS warehouse</t>
+  </si>
+  <si>
+    <t>COSB</t>
+  </si>
+  <si>
+    <t>Customs + Ocean + CFS warehouse</t>
+  </si>
+  <si>
+    <t>CSBB</t>
+  </si>
+  <si>
+    <t>Customs + CFS warehouse</t>
+  </si>
+  <si>
+    <t>TASB</t>
+  </si>
+  <si>
+    <t>Trucking + Air + CFS warehouse</t>
+  </si>
+  <si>
+    <t>TOSB</t>
+  </si>
+  <si>
+    <t>Trucking + Ocean + CFS warehouse</t>
+  </si>
+  <si>
+    <t>TSBB</t>
+  </si>
+  <si>
+    <t>Trucking + CFS warehouse</t>
+  </si>
+  <si>
+    <t>SBBB</t>
+  </si>
+  <si>
+    <t>CFS warehouse Only</t>
+  </si>
+  <si>
+    <t>ASBB</t>
+  </si>
+  <si>
+    <t>Air + CFS warehouse</t>
+  </si>
+  <si>
+    <t>OSBB</t>
+  </si>
+  <si>
+    <t>Ocean + CFS warehouse</t>
+  </si>
+  <si>
+    <t>CBTS</t>
+  </si>
+  <si>
+    <t>Cross-Border + CFS warehouse</t>
+  </si>
+  <si>
+    <t>FSBB</t>
+  </si>
+  <si>
+    <t>Booking Agent + CFS warehouse</t>
+  </si>
+  <si>
+    <t>FTSB</t>
+  </si>
+  <si>
+    <t>Booking Agent + Truck + CFS warehouse</t>
+  </si>
+  <si>
+    <t>FCSB</t>
+  </si>
+  <si>
+    <t>Booking Agent + Customs + CFS warehouse</t>
+  </si>
+  <si>
+    <t>FCTS</t>
+  </si>
+  <si>
+    <t>Booking Agent + Customs + Truck + CFS warehouse</t>
+  </si>
+  <si>
+    <t>CTAG</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + Air + General warehouse</t>
+  </si>
+  <si>
+    <t>CTOG</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + Ocean + General warehouse</t>
+  </si>
+  <si>
+    <t>CTGB</t>
+  </si>
+  <si>
+    <t>Customs + Trucking + General warehouse</t>
+  </si>
+  <si>
+    <t>CAGB</t>
+  </si>
+  <si>
+    <t>Customs + Air + General warehouse</t>
+  </si>
+  <si>
+    <t>COGB</t>
+  </si>
+  <si>
+    <t>Customs + Ocean + General warehouse</t>
+  </si>
+  <si>
+    <t>CGBB</t>
+  </si>
+  <si>
+    <t>Customs + General warehouse</t>
+  </si>
+  <si>
+    <t>TAGB</t>
+  </si>
+  <si>
+    <t>Trucking + Air + General warehouse</t>
+  </si>
+  <si>
+    <t>TOGB</t>
+  </si>
+  <si>
+    <t>Trucking + Ocean + General warehouse</t>
+  </si>
+  <si>
+    <t>TGBB</t>
+  </si>
+  <si>
+    <t>Trucking + General warehouse</t>
+  </si>
+  <si>
+    <t>GBBB</t>
+  </si>
+  <si>
+    <t>General warehouse Only</t>
+  </si>
+  <si>
+    <t>AGBB</t>
+  </si>
+  <si>
+    <t>Air + General warehouse</t>
+  </si>
+  <si>
+    <t>OGBB</t>
+  </si>
+  <si>
+    <t>Ocean + General warehouse</t>
+  </si>
+  <si>
+    <t>CBTG</t>
+  </si>
+  <si>
+    <t>Cross-Border + General warehouse</t>
+  </si>
+  <si>
+    <t>FGBB</t>
+  </si>
+  <si>
+    <t>Booking Agent + General warehouse</t>
+  </si>
+  <si>
+    <t>FTGB</t>
+  </si>
+  <si>
+    <t>Booking Agent + Truck + General warehouse</t>
+  </si>
+  <si>
+    <t>FCGB</t>
+  </si>
+  <si>
+    <t>Booking Agent + Customs + General warehouse</t>
+  </si>
+  <si>
+    <t>FCTG</t>
+  </si>
+  <si>
+    <t>Booking Agent + Customs + Truck + General warehouse</t>
+  </si>
+  <si>
+    <t>TTTB</t>
+  </si>
+  <si>
+    <t>Truck Sea Truck</t>
+  </si>
+  <si>
+    <t>TTBB</t>
+  </si>
+  <si>
+    <t>Truck Air Truck</t>
+  </si>
+  <si>
+    <t>AECO</t>
+  </si>
+  <si>
+    <t>CO only</t>
+  </si>
+  <si>
+    <t>DECO</t>
+  </si>
+  <si>
+    <t>OEFCLCO</t>
+  </si>
+  <si>
+    <t>OELCLCO</t>
   </si>
 </sst>
 </file>
@@ -4264,7 +4877,7 @@
     <numFmt numFmtId="167" formatCode="#,##0.00;\-#,##0.00;\-"/>
     <numFmt numFmtId="168" formatCode="[$-409]mmm\-yy;@"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4366,8 +4979,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4426,8 +5045,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -4513,6 +5138,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -4522,7 +5158,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4891,6 +5527,12 @@
     <xf numFmtId="16" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -4900,7 +5542,17 @@
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
     <cellStyle name="標準_1問題1シートBlank" xfId="4" xr:uid="{A683D387-F1ED-42C3-928D-68831043DFA8}"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -7028,16 +7680,16 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="P3:P707">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>$P3="Low Load"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="9" priority="2">
       <formula>$P3="Balanced"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="3">
+    <cfRule type="expression" dxfId="8" priority="3">
       <formula>$P3="High Load"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="4">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>$P3="Overload"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -32487,7 +33139,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3:C7">
-    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -33175,16 +33827,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3:C4">
-    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:C9">
-    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:C16">
-    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17:C20">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -33808,6 +34460,851 @@
       <c r="Q18" s="134"/>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{064E9516-A861-4A2F-A95A-9DDA6A969784}">
+  <dimension ref="A1:B104"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="12.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="139" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="18" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="18" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="18" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="18" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="18" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="18" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="18" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="18" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="18" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="18" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="18" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="18" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="18" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="18" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="18" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="18" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="18" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="18" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="18" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="18" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="18" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="18" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="18" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="18" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="18" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="18" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="18" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="18" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="18" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="18" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="18" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="18" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="18" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="18" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="18" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="18" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="18" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="18" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="18" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="18" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="18" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="18" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="18" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="18" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B46" s="18" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="18" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="18" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="18" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="136" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B50" s="136" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="18" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="18" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B52" s="18" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="18" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="136" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B54" s="136" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="137" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="137" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B56" s="18" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="137" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B57" s="18" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="137" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B58" s="18" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="137" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B59" s="18" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="137" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B60" s="18" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="137" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="137" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="137" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B63" s="18" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="137" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B64" s="136" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="136" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B65" s="136" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="136" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B66" s="136" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="136" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B67" s="136" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="136" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B68" s="136" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="136" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B69" s="136" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="136" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B70" s="136" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="136" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B71" s="136" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="136" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B72" s="136" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="136" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B73" s="136" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="136" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B74" s="136" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="136" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B75" s="136" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="136" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B76" s="136" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="136" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B77" s="136" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="136" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B78" s="136" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="136" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B79" s="136" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="136" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B80" s="136" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="136" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B81" s="136" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="136" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B82" s="136" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="136" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B83" s="136" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="136" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B84" s="136" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="136" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B85" s="136" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="136" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B86" s="136" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="136" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B87" s="136" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="136" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B88" s="136" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="136" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B89" s="136" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="136" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B90" s="136" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="136" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B91" s="136" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="136" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B92" s="136" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="136" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B93" s="136" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="136" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B94" s="136" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="136" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B95" s="136" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="136" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B96" s="136" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="136" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B97" s="136" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="136" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B98" s="136" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="136" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B99" s="136" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="136" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B100" s="136" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="18" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B101" s="138" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="136" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B102" s="138" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="136" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B103" s="138" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="136" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B104" s="138" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A101">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -36395,7 +37892,7 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
